--- a/artfynd/A 44489-2024 artfynd.xlsx
+++ b/artfynd/A 44489-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134971474</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134968589</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134960396</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134961052</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134966902</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134960184</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1359,6 +1394,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134956474</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1465,6 +1505,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134957094</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1562,6 +1607,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134960395</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1659,6 +1709,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134958435</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1760,6 +1815,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134968172</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1857,6 +1917,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134969012</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1954,6 +2019,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134969222</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2051,8 +2121,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134963668</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 44489-2024 artfynd.xlsx
+++ b/artfynd/A 44489-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134971474</v>
       </c>
       <c r="B2" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>134968589</v>
       </c>
       <c r="B3" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>134960396</v>
       </c>
       <c r="B4" t="n">
-        <v>80492</v>
+        <v>80530</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>134960184</v>
       </c>
       <c r="B7" t="n">
-        <v>99103</v>
+        <v>99150</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>134956474</v>
       </c>
       <c r="B8" t="n">
-        <v>99099</v>
+        <v>99146</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>134957094</v>
       </c>
       <c r="B9" t="n">
-        <v>99099</v>
+        <v>99146</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>134960395</v>
       </c>
       <c r="B10" t="n">
-        <v>99099</v>
+        <v>99146</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>134958435</v>
       </c>
       <c r="B11" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>134968172</v>
       </c>
       <c r="B12" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>134969012</v>
       </c>
       <c r="B13" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>134969222</v>
       </c>
       <c r="B14" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>134963668</v>
       </c>
       <c r="B15" t="n">
-        <v>100220</v>
+        <v>100267</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
